--- a/tame_output/ON/bt/strategyON_20231124.xlsx
+++ b/tame_output/ON/bt/strategyON_20231124.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.0%</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.0%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.9%</t>
+          <t>131.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1790"/>
+  <dimension ref="A1:G1791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.144989065675285</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42696,6 +42696,29 @@
       </c>
       <c r="G1790" t="n">
         <v>4.378233029941786</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="2" t="n">
+        <v>45253</v>
+      </c>
+      <c r="B1791" t="n">
+        <v>3.145659693631203</v>
+      </c>
+      <c r="C1791" t="n">
+        <v>3.072322299854575</v>
+      </c>
+      <c r="D1791" t="n">
+        <v>1.55532339303798</v>
+      </c>
+      <c r="E1791" t="n">
+        <v>3.69409523275602</v>
+      </c>
+      <c r="F1791" t="n">
+        <v>2.176385105634913</v>
+      </c>
+      <c r="G1791" t="n">
+        <v>4.378153363235525</v>
       </c>
     </row>
   </sheetData>
